--- a/formula_excel.xlsx
+++ b/formula_excel.xlsx
@@ -18,22 +18,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Author</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Formula</t>
+    <t>TITLE</t>
+  </si>
+  <si>
+    <t>AUTHOR</t>
+  </si>
+  <si>
+    <t>YEAR</t>
+  </si>
+  <si>
+    <t>PRICE</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>FORMULA</t>
   </si>
   <si>
     <t xml:space="preserve">WordPress 5</t>
@@ -665,7 +665,7 @@
         <v>44479</v>
       </c>
       <c r="F2">
-        <f>SUM(D5:D6)</f>
+        <f>SUM(G5:G6)</f>
         <v>57.445900000000002</v>
       </c>
     </row>
@@ -701,12 +701,12 @@
       </c>
     </row>
     <row r="5" ht="16.5">
-      <c r="D5">
+      <c r="G5">
         <v>11.568899999999999</v>
       </c>
     </row>
     <row r="6" ht="16.5">
-      <c r="D6">
+      <c r="G6">
         <v>45.877000000000002</v>
       </c>
     </row>
